--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0001.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0001.xlsx
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Makt delas mellan alla partier</t>
+          <t>Makt delas mellan flera partier</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Domstolar styr landet</t>
+          <t>Domstolarna har avgörande makt</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Kommuner styr allt</t>
+          <t>Kommunerna har mycket självstyre</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Ger bara stöd till rika</t>
+          <t>Bygger främst på privata försäkringar</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Har inga skatter</t>
+          <t>Har låg offentlig sektor och få tjänster</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Förbjuder social trygghet</t>
+          <t>Låter familjen ta huvudansvaret</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Period med noll skatter</t>
+          <t>Period med låg tillväxt och fallande efterfrågan</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Ökning av priser utan risker</t>
+          <t>Kraftig nedgång i BNP och investeringar</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Hur många bilar per hushåll</t>
+          <t>Andel sysselsatta i befolkningen</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Antal sjöar i landet</t>
+          <t>Relationen mellan inkomster och utgifter</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Hur många språk som talas</t>
+          <t>Antal personer per hushåll</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Ingen i arbetsålder alls</t>
+          <t>Fler pensionärer per 100 i arbetsålder</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Endast pensionärer i landet</t>
+          <t>Fler barn per 100 i arbetsålder</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Skidvädret i Lappland</t>
+          <t>Lönernas nivå</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Antal val per år</t>
+          <t>Exportindustrins konkurrenskraft</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Antal öar i skärgården</t>
+          <t>Bostadsmarknadens prisutveckling</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Endast mer snö</t>
+          <t>Förändringar i väder från år till år</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Fler cyklar</t>
+          <t>Solvariationer</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Mindre internet</t>
+          <t>Vulkanutbrott</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Ökad läsning</t>
+          <t>Jordbanans variationer</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Fler sjöar</t>
+          <t>Solvariationer</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Mindre vind</t>
+          <t>Vulkanutbrott</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Fler språk</t>
+          <t>Naturliga klimatcykler</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Månens faser</t>
+          <t>Solaktivitet</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Vulkaner i Finland</t>
+          <t>Naturliga klimatcykler</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Havsströmmar i Östersjön</t>
+          <t>Jordbanans variationer</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Den fanns inte alls</t>
+          <t>Den minskade gradvis under 1920-talet</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Den var bara i utlandet</t>
+          <t>Den var mindre än före kriget</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Den löstes direkt samma år</t>
+          <t>Den berodde främst på språkfrågan</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>De vann kriget</t>
+          <t>De förlorade politiskt inflytande</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>De hade mer pengar</t>
+          <t>De fick hårdare straff och fängelsedomar</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>De ville avskaffa val</t>
+          <t>De kände sig orättvist behandlade efter kriget</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>De kämpade för att bli en del av Sverige</t>
+          <t>De försvarade lag och ordning</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>De ville avskaffa Finland</t>
+          <t>De ville hindra en revolution</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>De ville bli en del av Tyskland</t>
+          <t>De såg sig som skydd mot bolsjevism</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Som ett religionskrig</t>
+          <t>Som en kamp om demokrati</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Som ett kolonialkrig</t>
+          <t>Som en socialistisk revolution</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Som ett sportkrig</t>
+          <t>Som en kamp om arbetsvillkor</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot skola</t>
+          <t>Skolan blev frivillig</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Privat skola för alla</t>
+          <t>Större fokus på yrkesutbildning</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Endast universitet</t>
+          <t>Förkortad skolplikt</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Ingen skatt</t>
+          <t>Proportionell beskattning</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Skatt bara på mat</t>
+          <t>Högre indirekta skatter</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Arbetsförbud</t>
+          <t>Tio timmars arbetsdag</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Arbete bara på helger</t>
+          <t>Sex timmars arbetsdag</t>
         </is>
       </c>
       <c r="G28" s="14" t="n">
